--- a/hira_material_automation/output/monthly/202601_202607__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__arthroscopy_cannula__041001__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:02:33</t>
+          <t>2026-07-14T22:02:25</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fd11d3072912325c678c923aac6cf227b200ccfe7a9930fc5e24f333ac4f6e91</t>
+          <t>09f4b5a6653ec40d0de0a257090cd64f84ca990b663c7d74cf71d8a2d685e96c</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__arthroscopy_cannula__041001__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:02:25</t>
+          <t>2026-07-24T22:09:19</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09f4b5a6653ec40d0de0a257090cd64f84ca990b663c7d74cf71d8a2d685e96c</t>
+          <t>6977710c3c86b85d94c8266e5c19e553b4f3b6184dc986bb33ca3ec12ffb9a4e</t>
         </is>
       </c>
     </row>
